--- a/clients/大晃産業/03_日程調整/【日程調整】管理職候補育成プログラム_全12回日程表.xlsx
+++ b/clients/大晃産業/03_日程調整/【日程調整】管理職候補育成プログラム_全12回日程表.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,17 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +72,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0C4"/>
+        <bgColor rgb="FFFFF0C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -108,6 +123,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,7 +511,7 @@
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -502,7 +526,7 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>※ご希望の日程に○をご記入ください。可能な限り同じ曜日に揃えることが望ましいです。</t>
+          <t>※各回の「選択」列の▼をクリックし、ご希望の候補日を選択してください。各回の間隔が約1ヶ月程度空くようご調整をお願いいたします。</t>
         </is>
       </c>
     </row>
@@ -552,10 +576,10 @@
           <t>曜日③</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>ご希望
-（○をご記入）</t>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>選択
+（▼で選択）</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -607,7 +631,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="J5" s="10" t="n"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
           <t>9:00〜17:00</t>
@@ -653,7 +677,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="J6" s="10" t="n"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>9:00〜17:00</t>
@@ -699,7 +723,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="10" t="n"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
           <t>9:00〜17:00</t>
@@ -745,7 +769,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="J8" s="10" t="n"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>9:00〜17:00</t>
@@ -791,7 +815,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
+      <c r="J9" s="10" t="n"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>9:00〜17:00</t>
@@ -837,7 +861,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
+      <c r="J10" s="10" t="n"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
           <t>9:00〜17:00</t>
@@ -883,7 +907,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
+      <c r="J11" s="10" t="n"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
           <t>9:00〜17:00</t>
@@ -929,7 +953,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr"/>
       <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
+      <c r="J12" s="10" t="n"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
           <t>9:00〜17:00</t>
@@ -975,7 +999,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
+      <c r="J13" s="10" t="n"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
           <t>9:00〜17:00</t>
@@ -1021,7 +1045,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr"/>
       <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
+      <c r="J14" s="10" t="n"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
           <t>9:00〜17:00</t>
@@ -1067,7 +1091,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
+      <c r="J15" s="10" t="n"/>
       <c r="K15" s="6" t="inlineStr">
         <is>
           <t>DAY1: 9:00〜17:00 / DAY2: 8:30〜15:00</t>
@@ -1117,7 +1141,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr"/>
       <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="4" t="inlineStr"/>
+      <c r="J16" s="10" t="n"/>
       <c r="K16" s="4" t="inlineStr">
         <is>
           <t>9:00〜17:00</t>
@@ -1159,16 +1183,18 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・会場候補: [                    ]（ご記入ください）</t>
-        </is>
-      </c>
+          <t xml:space="preserve">　・会場候補:</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・実施可否: 実施する / 実施しない（いずれかに○）</t>
-        </is>
-      </c>
+          <t xml:space="preserve">　・実施可否:</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1182,6 +1208,14 @@
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="J5:J16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="候補日①、候補日②、候補日③のいずれかを選択してください。" promptTitle="日程選択" prompt="▼を押してご希望の候補日を選択してください" type="list">
+      <formula1>"候補日①,候補日②,候補日③"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="合宿実施可否" prompt="▼を押して選択してください" type="list">
+      <formula1>"実施する,実施しない"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
